--- a/vignettes/vignette-2/target_transition_table.xlsx
+++ b/vignettes/vignette-2/target_transition_table.xlsx
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>726</v>
+        <v>752</v>
       </c>
       <c r="O2" t="n">
-        <v>430</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/target_transition_table.xlsx
+++ b/vignettes/vignette-2/target_transition_table.xlsx
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>752</v>
+        <v>695</v>
       </c>
       <c r="O2" t="n">
-        <v>404</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/target_transition_table.xlsx
+++ b/vignettes/vignette-2/target_transition_table.xlsx
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>695</v>
+        <v>678</v>
       </c>
       <c r="O2" t="n">
-        <v>385</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/target_transition_table.xlsx
+++ b/vignettes/vignette-2/target_transition_table.xlsx
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="O2" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/target_transition_table.xlsx
+++ b/vignettes/vignette-2/target_transition_table.xlsx
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="O2" t="n">
-        <v>372</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/target_transition_table.xlsx
+++ b/vignettes/vignette-2/target_transition_table.xlsx
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="O2" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/target_transition_table.xlsx
+++ b/vignettes/vignette-2/target_transition_table.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="O2" t="n">
         <v>376</v>

--- a/vignettes/vignette-2/target_transition_table.xlsx
+++ b/vignettes/vignette-2/target_transition_table.xlsx
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="O2" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/target_transition_table.xlsx
+++ b/vignettes/vignette-2/target_transition_table.xlsx
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>695</v>
+        <v>674</v>
       </c>
       <c r="O2" t="n">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/target_transition_table.xlsx
+++ b/vignettes/vignette-2/target_transition_table.xlsx
@@ -549,7 +549,7 @@
         <v>674</v>
       </c>
       <c r="O2" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/target_transition_table.xlsx
+++ b/vignettes/vignette-2/target_transition_table.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="O2" t="n">
         <v>368</v>

--- a/vignettes/vignette-2/target_transition_table.xlsx
+++ b/vignettes/vignette-2/target_transition_table.xlsx
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>672</v>
+        <v>649</v>
       </c>
       <c r="O2" t="n">
-        <v>368</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/target_transition_table.xlsx
+++ b/vignettes/vignette-2/target_transition_table.xlsx
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="O2" t="n">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/target_transition_table.xlsx
+++ b/vignettes/vignette-2/target_transition_table.xlsx
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="O2" t="n">
-        <v>394</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
